--- a/res/标签大全.xlsx
+++ b/res/标签大全.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bread\Workplace\Python\Binary\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\PythonWorkplace\Probability\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9CDA4C-72DD-4C4D-AE5C-68926AC390CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32992343-2CCF-42B5-BA00-2AD9A6465749}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{51AAA0D9-229E-4E49-83B0-5342FE57A35A}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="41490" windowHeight="16770" xr2:uid="{51AAA0D9-229E-4E49-83B0-5342FE57A35A}"/>
   </bookViews>
   <sheets>
     <sheet name="160" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -44,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="60">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,6 +224,10 @@
   <si>
     <t>双结算锦囊</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害锦囊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -452,12 +445,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC005F87-753C-4035-AF28-88921D0D29EA}" name="表1_4" displayName="表1_4" ref="A1:R161" totalsRowShown="0">
-  <autoFilter ref="A1:R161" xr:uid="{516B080F-E782-44DC-9583-A7A64AC02D85}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R161">
-    <sortCondition ref="B1:B161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC005F87-753C-4035-AF28-88921D0D29EA}" name="表1_4" displayName="表1_4" ref="A1:S161" totalsRowShown="0">
+  <autoFilter ref="A1:S161" xr:uid="{516B080F-E782-44DC-9583-A7A64AC02D85}"/>
+  <sortState ref="A2:S161">
+    <sortCondition descending="1" ref="B1:B161"/>
   </sortState>
-  <tableColumns count="18">
+  <tableColumns count="19">
     <tableColumn id="12" xr3:uid="{64BBCE38-5936-4C87-AF10-3349147B669B}" name="id"/>
     <tableColumn id="2" xr3:uid="{2EB3C21C-5941-4E90-97BD-C27CBE419CE0}" name="name"/>
     <tableColumn id="7" xr3:uid="{F4F1965D-5402-4058-98C7-57132F18887D}" name="color" dataDxfId="5"/>
@@ -474,6 +467,7 @@
     <tableColumn id="9" xr3:uid="{4FF0B498-311B-4782-BACC-D5B8631F833A}" name="attDistance"/>
     <tableColumn id="10" xr3:uid="{BC677E26-FD68-45B3-B840-8749FEFDF591}" name="defDistance"/>
     <tableColumn id="11" xr3:uid="{A05B0A1A-53BB-4EFD-AC2D-FC62A816498E}" name="spellId"/>
+    <tableColumn id="17" xr3:uid="{01904350-CF67-406B-9185-6A169A39D612}" name="伤害锦囊"/>
     <tableColumn id="16" xr3:uid="{71E82C6F-E7AE-48BC-A3CC-E496035B7A55}" name="颅行" dataDxfId="0" dataCellStyle="常规 2"/>
     <tableColumn id="1" xr3:uid="{3C81F222-E66B-4540-92F8-0ED6D2BD9443}" name="锦囊"/>
     <tableColumn id="5" xr3:uid="{7B1355E0-1CAA-49A6-9305-23A896CD5642}" name="双结算锦囊"/>
@@ -688,22 +682,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D04EA50-A07E-49F2-BF5D-56302F8712A2}">
-  <dimension ref="A1:R161"/>
-  <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:S161"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.05078125" customWidth="1"/>
-    <col min="2" max="2" width="12.41796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.05078125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.68359375" customWidth="1"/>
-    <col min="5" max="5" width="3.41796875" customWidth="1"/>
-    <col min="6" max="6" width="5.734375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.734375" customWidth="1"/>
+    <col min="1" max="1" width="6.06640625" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.06640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" customWidth="1"/>
+    <col min="6" max="6" width="5.73046875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5234375" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -741,86 +735,89 @@
         <v>8</v>
       </c>
       <c r="M1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
+      </c>
+      <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>装备</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="D2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>16</v>
-      </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="N2" s="6"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S2" s="4"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>3</v>
-      </c>
-      <c r="D3" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <v>3</v>
@@ -830,10 +827,10 @@
         <v>装备</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -842,21 +839,21 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>16</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="N3" s="6"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3">
         <v>4</v>
@@ -876,10 +873,10 @@
         <v>装备</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -888,108 +885,123 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>89</v>
-      </c>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+        <v>23</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3">
-        <v>3</v>
-      </c>
-      <c r="D5" t="str">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>装备</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>87</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>52</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3</v>
+      </c>
+      <c r="G6" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>装备</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>103</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3</v>
+      </c>
+      <c r="D7" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
         <v>♠</v>
       </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3">
-        <v>2</v>
-      </c>
-      <c r="G5" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>84</v>
-      </c>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>151</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="3">
-        <v>4</v>
-      </c>
-      <c r="D6" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
-      <c r="G6" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>84</v>
-      </c>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>31</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
       <c r="E7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F7" s="3">
         <v>3</v>
@@ -999,56 +1011,56 @@
         <v>装备</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>17</v>
-      </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="N7" s="6"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S7" s="4"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1057,87 +1069,97 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>24</v>
-      </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S8" s="4"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3">
-        <v>3</v>
-      </c>
-      <c r="D9" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>19</v>
-      </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S9" s="4"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3">
-        <v>4</v>
-      </c>
-      <c r="D10" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1146,47 +1168,54 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>21</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S10" s="4"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>♥</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1195,44 +1224,51 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>29</v>
-      </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S11" s="4"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3">
-        <v>3</v>
-      </c>
-      <c r="D12" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1241,39 +1277,51 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>86</v>
-      </c>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>♥</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1282,28 +1330,35 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>28</v>
-      </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>4</v>
+      </c>
+      <c r="D14" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E14">
         <v>12</v>
@@ -1328,27 +1383,24 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>5</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S14" s="4"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3">
         <v>4</v>
@@ -1358,7 +1410,7 @@
         <v>♣</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3">
         <v>2</v>
@@ -1380,37 +1432,34 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>5</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S15" s="4"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>♠</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F16" s="3">
         <v>2</v>
@@ -1432,34 +1481,31 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>5</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S16" s="4"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3">
-        <v>3</v>
-      </c>
-      <c r="D17" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E17">
         <v>12</v>
@@ -1484,37 +1530,34 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>5</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S17" s="4"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3">
-        <v>3</v>
-      </c>
-      <c r="D18" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" s="3">
         <v>2</v>
@@ -1536,37 +1579,34 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>5</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S18" s="4"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3">
-        <v>3</v>
-      </c>
-      <c r="D19" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3">
         <v>2</v>
@@ -1588,27 +1628,24 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>5</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S19" s="4"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3">
         <v>3</v>
@@ -1618,20 +1655,20 @@
         <v>♠</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1640,41 +1677,36 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>201</v>
-      </c>
-      <c r="M20" s="6"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>♥</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F21" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1683,29 +1715,41 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>90</v>
-      </c>
-      <c r="M21" s="6"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C22" s="3">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D22" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F22" s="3">
         <v>2</v>
@@ -1727,35 +1771,28 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>83</v>
-      </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D23" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F23" s="3">
         <v>2</v>
@@ -1777,35 +1814,28 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>83</v>
-      </c>
-      <c r="M23" s="6"/>
-      <c r="N23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D24" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3">
         <v>2</v>
@@ -1827,16 +1857,18 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>83</v>
-      </c>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C25" s="3">
         <v>4</v>
@@ -1846,7 +1878,7 @@
         <v>♣</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" s="3">
         <v>2</v>
@@ -1868,23 +1900,18 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>14</v>
-      </c>
-      <c r="M25" s="6"/>
-      <c r="N25" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C26" s="3">
         <v>4</v>
@@ -1894,226 +1921,224 @@
         <v>♣</v>
       </c>
       <c r="E26">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2</v>
+      </c>
+      <c r="G26" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>85</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>160</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="3">
+        <v>4</v>
+      </c>
+      <c r="D27" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E27">
         <v>13</v>
       </c>
-      <c r="F26" s="3">
-        <v>2</v>
-      </c>
-      <c r="G26" t="str">
+      <c r="F27" s="3">
+        <v>2</v>
+      </c>
+      <c r="G27" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
         <v>锦囊</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>14</v>
-      </c>
-      <c r="M26" s="6"/>
-      <c r="N26" s="4" t="s">
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>85</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>136</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3</v>
+      </c>
+      <c r="D28" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>3</v>
+      </c>
+      <c r="G28" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>装备</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>88</v>
+      </c>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>149</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="3">
+        <v>4</v>
+      </c>
+      <c r="D29" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3</v>
+      </c>
+      <c r="G29" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>装备</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>88</v>
+      </c>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>40</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>2</v>
+      </c>
+      <c r="G30" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>12</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A27">
-        <v>130</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="3">
-        <v>2</v>
-      </c>
-      <c r="D27" s="2" t="str">
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
         <v>♦</v>
       </c>
-      <c r="E27">
-        <v>9</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1</v>
-      </c>
-      <c r="G27" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>82</v>
-      </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A28">
-        <v>137</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="3">
-        <v>3</v>
-      </c>
-      <c r="D28" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
-      </c>
-      <c r="E28">
-        <v>3</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>82</v>
-      </c>
-      <c r="M28" s="6"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A29">
-        <v>143</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="3">
-        <v>3</v>
-      </c>
-      <c r="D29" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
-      </c>
-      <c r="E29">
-        <v>9</v>
-      </c>
-      <c r="F29" s="3">
-        <v>1</v>
-      </c>
-      <c r="G29" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>82</v>
-      </c>
-      <c r="M29" s="6"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A30">
-        <v>150</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="3">
-        <v>4</v>
-      </c>
-      <c r="D30" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
-      <c r="E30">
-        <v>3</v>
-      </c>
-      <c r="F30" s="3">
-        <v>1</v>
-      </c>
-      <c r="G30" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>82</v>
-      </c>
-      <c r="M30" s="6"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A31">
-        <v>156</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="3">
-        <v>4</v>
-      </c>
-      <c r="D31" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
       <c r="E31">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -2135,33 +2160,40 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>82</v>
-      </c>
-      <c r="M31" s="6"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+        <v>3</v>
+      </c>
+      <c r="N31" s="6"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S31" s="4"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C32" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>♥</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2176,42 +2208,40 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>8</v>
-      </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N32" s="6"/>
+      <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S32" s="4"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
+      </c>
+      <c r="E33">
         <v>4</v>
       </c>
-      <c r="D33" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
       <c r="F33" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2226,42 +2256,40 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>8</v>
-      </c>
-      <c r="M33" s="6"/>
-      <c r="N33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N33" s="6"/>
+      <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S33" s="4"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C34" s="3">
-        <v>3</v>
-      </c>
-      <c r="D34" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F34" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2276,45 +2304,43 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>8</v>
-      </c>
-      <c r="M34" s="6"/>
-      <c r="N34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O34" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="4"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S34" s="4"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F35" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>基本</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2323,24 +2349,26 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>20</v>
-      </c>
-      <c r="M35" s="6"/>
-      <c r="N35" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N35" s="6"/>
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S35" s="4"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -2350,17 +2378,17 @@
         <v>♥</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F36" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2372,43 +2400,43 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>15</v>
-      </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N36" s="6"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S36" s="4"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C37" s="3">
-        <v>4</v>
-      </c>
-      <c r="D37" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2420,43 +2448,43 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>15</v>
-      </c>
-      <c r="M37" s="6"/>
-      <c r="N37" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N37" s="6"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S37" s="4"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C38" s="3">
-        <v>3</v>
-      </c>
-      <c r="D38" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F38" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2468,40 +2496,40 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>15</v>
-      </c>
-      <c r="M38" s="6"/>
-      <c r="N38" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N38" s="6"/>
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S38" s="4"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C39" s="3">
-        <v>4</v>
-      </c>
-      <c r="D39" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2516,42 +2544,40 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>9</v>
-      </c>
-      <c r="M39" s="6"/>
-      <c r="N39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N39" s="6"/>
+      <c r="O39" s="4"/>
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S39" s="4"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C40" s="3">
-        <v>3</v>
-      </c>
-      <c r="D40" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2566,42 +2592,40 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>9</v>
-      </c>
-      <c r="M40" s="6"/>
-      <c r="N40" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N40" s="6"/>
+      <c r="O40" s="4"/>
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S40" s="4"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C41" s="3">
-        <v>3</v>
-      </c>
-      <c r="D41" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E41">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F41" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2616,48 +2640,46 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>9</v>
-      </c>
-      <c r="M41" s="6"/>
-      <c r="N41" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N41" s="6"/>
+      <c r="O41" s="4"/>
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S41" s="4"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>基本</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2666,44 +2688,46 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>30</v>
-      </c>
-      <c r="M42" s="6"/>
-      <c r="N42" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N42" s="6"/>
       <c r="O42" s="4"/>
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S42" s="4"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C43" s="3">
-        <v>3</v>
-      </c>
-      <c r="D43" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F43" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2712,44 +2736,51 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>25</v>
-      </c>
-      <c r="M43" s="6"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S43" s="4"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C44" s="3">
-        <v>3</v>
-      </c>
-      <c r="D44" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>锦囊</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -2758,84 +2789,98 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>26</v>
-      </c>
-      <c r="M44" s="6"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S44" s="4"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C45" s="3">
+        <v>3</v>
+      </c>
+      <c r="D45" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2</v>
+      </c>
+      <c r="G45" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
         <v>4</v>
       </c>
-      <c r="D45" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3</v>
-      </c>
-      <c r="G45" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
-      </c>
-      <c r="H45">
-        <v>2</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>200</v>
-      </c>
-      <c r="M45" s="6"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S45" s="4"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C46" s="3">
-        <v>2</v>
-      </c>
-      <c r="D46" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D46" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2850,40 +2895,45 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>1</v>
-      </c>
-      <c r="M46" s="6"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4" t="s">
-        <v>53</v>
+        <v>4</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S46" s="4"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C47" s="3">
-        <v>2</v>
-      </c>
-      <c r="D47" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D47" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E47">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -2898,43 +2948,48 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>1</v>
-      </c>
-      <c r="M47" s="6"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4" t="s">
-        <v>53</v>
+        <v>4</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P47" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S47" s="4"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C48" s="3">
-        <v>2</v>
-      </c>
-      <c r="D48" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D48" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E48">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2946,43 +3001,44 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>1</v>
-      </c>
-      <c r="M48" s="6"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S48" s="4"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>♥</v>
       </c>
       <c r="E49">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2994,24 +3050,25 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1</v>
-      </c>
-      <c r="M49" s="6"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
       <c r="R49" s="4"/>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S49" s="4"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50">
+        <v>2</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C50" s="3">
         <v>2</v>
       </c>
@@ -3020,7 +3077,7 @@
         <v>♦</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F50" s="3">
         <v>1</v>
@@ -3042,23 +3099,21 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>1</v>
-      </c>
-      <c r="M50" s="6"/>
-      <c r="N50" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N50" s="6"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S50" s="4"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C51" s="3">
         <v>2</v>
@@ -3068,7 +3123,7 @@
         <v>♦</v>
       </c>
       <c r="E51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F51" s="3">
         <v>1</v>
@@ -3090,33 +3145,31 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>1</v>
-      </c>
-      <c r="M51" s="6"/>
-      <c r="N51" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N51" s="6"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S51" s="4"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C52" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E52">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F52" s="3">
         <v>1</v>
@@ -3138,33 +3191,31 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>1</v>
-      </c>
-      <c r="M52" s="6"/>
-      <c r="N52" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N52" s="6"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S52" s="4"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C53" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E53">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F53" s="3">
         <v>1</v>
@@ -3186,33 +3237,31 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>1</v>
-      </c>
-      <c r="M53" s="6"/>
-      <c r="N53" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N53" s="6"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S53" s="4"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C54" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E54">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F54" s="3">
         <v>1</v>
@@ -3234,33 +3283,31 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>1</v>
-      </c>
-      <c r="M54" s="6"/>
-      <c r="N54" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N54" s="6"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S54" s="4"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C55" s="3">
-        <v>4</v>
-      </c>
-      <c r="D55" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>2</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F55" s="3">
         <v>1</v>
@@ -3282,33 +3329,31 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>1</v>
-      </c>
-      <c r="M55" s="6"/>
-      <c r="N55" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N55" s="6"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S55" s="4"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C56" s="3">
-        <v>4</v>
-      </c>
-      <c r="D56" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>2</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3">
         <v>1</v>
@@ -3330,33 +3375,31 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>1</v>
-      </c>
-      <c r="M56" s="6"/>
-      <c r="N56" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N56" s="6"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
       <c r="R56" s="4"/>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S56" s="4"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C57" s="3">
-        <v>4</v>
-      </c>
-      <c r="D57" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>2</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F57" s="3">
         <v>1</v>
@@ -3378,33 +3421,31 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1</v>
-      </c>
-      <c r="M57" s="6"/>
-      <c r="N57" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N57" s="6"/>
       <c r="O57" s="4"/>
-      <c r="P57" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S57" s="4"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C58" s="3">
-        <v>4</v>
-      </c>
-      <c r="D58" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>2</v>
+      </c>
+      <c r="D58" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
@@ -3426,33 +3467,31 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>1</v>
-      </c>
-      <c r="M58" s="6"/>
-      <c r="N58" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N58" s="6"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
       <c r="R58" s="4"/>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S58" s="4"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C59" s="3">
-        <v>4</v>
-      </c>
-      <c r="D59" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>2</v>
+      </c>
+      <c r="D59" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
@@ -3474,33 +3513,31 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>1</v>
-      </c>
-      <c r="M59" s="6"/>
-      <c r="N59" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N59" s="6"/>
       <c r="O59" s="4"/>
-      <c r="P59" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S59" s="4"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C60" s="3">
-        <v>4</v>
-      </c>
-      <c r="D60" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>2</v>
+      </c>
+      <c r="D60" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E60">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3">
         <v>1</v>
@@ -3522,33 +3559,31 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>1</v>
-      </c>
-      <c r="M60" s="6"/>
-      <c r="N60" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N60" s="6"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
       <c r="R60" s="4"/>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S60" s="4"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C61" s="3">
-        <v>4</v>
-      </c>
-      <c r="D61" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>2</v>
+      </c>
+      <c r="D61" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="3">
         <v>1</v>
@@ -3570,33 +3605,31 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>1</v>
-      </c>
-      <c r="M61" s="6"/>
-      <c r="N61" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N61" s="6"/>
       <c r="O61" s="4"/>
-      <c r="P61" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
       <c r="R61" s="4"/>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S61" s="4"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C62" s="3">
-        <v>4</v>
-      </c>
-      <c r="D62" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E62">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F62" s="3">
         <v>1</v>
@@ -3618,34 +3651,32 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>1</v>
-      </c>
-      <c r="M62" s="6"/>
-      <c r="N62" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N62" s="6"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P62" s="4"/>
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S62" s="4"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
+      </c>
+      <c r="E63">
         <v>13</v>
       </c>
-      <c r="C63" s="3">
-        <v>4</v>
-      </c>
-      <c r="D63" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
-      <c r="E63">
-        <v>10</v>
-      </c>
       <c r="F63" s="3">
         <v>1</v>
       </c>
@@ -3666,33 +3697,31 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>1</v>
-      </c>
-      <c r="M63" s="6"/>
-      <c r="N63" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N63" s="6"/>
       <c r="O63" s="4"/>
-      <c r="P63" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P63" s="4"/>
       <c r="Q63" s="4"/>
       <c r="R63" s="4"/>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S63" s="4"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C64" s="3">
-        <v>4</v>
-      </c>
-      <c r="D64" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E64">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F64" s="3">
         <v>1</v>
@@ -3714,30 +3743,28 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>1</v>
-      </c>
-      <c r="M64" s="6"/>
-      <c r="N64" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N64" s="6"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
       <c r="R64" s="4"/>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S64" s="4"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C65" s="3">
-        <v>4</v>
-      </c>
-      <c r="D65" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E65">
         <v>8</v>
@@ -3762,30 +3789,28 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>1</v>
-      </c>
-      <c r="M65" s="6"/>
-      <c r="N65" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N65" s="6"/>
       <c r="O65" s="4"/>
-      <c r="P65" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
       <c r="R65" s="4"/>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S65" s="4"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C66" s="3">
-        <v>4</v>
-      </c>
-      <c r="D66" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E66">
         <v>9</v>
@@ -3810,33 +3835,31 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>1</v>
-      </c>
-      <c r="M66" s="6"/>
-      <c r="N66" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N66" s="6"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
       <c r="R66" s="4"/>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S66" s="4"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C67" s="3">
-        <v>4</v>
-      </c>
-      <c r="D67" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F67" s="3">
         <v>1</v>
@@ -3858,33 +3881,31 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>1</v>
-      </c>
-      <c r="M67" s="6"/>
-      <c r="N67" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N67" s="6"/>
       <c r="O67" s="4"/>
-      <c r="P67" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
       <c r="R67" s="4"/>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S67" s="4"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C68" s="3">
-        <v>4</v>
-      </c>
-      <c r="D68" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E68">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F68" s="3">
         <v>1</v>
@@ -3906,33 +3927,31 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="M68" s="6"/>
-      <c r="N68" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N68" s="6"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
       <c r="R68" s="4"/>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S68" s="4"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C69" s="3">
-        <v>3</v>
-      </c>
-      <c r="D69" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D69" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F69" s="3">
         <v>1</v>
@@ -3954,33 +3973,31 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>1</v>
-      </c>
-      <c r="M69" s="6"/>
-      <c r="N69" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N69" s="6"/>
       <c r="O69" s="4"/>
-      <c r="P69" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
       <c r="R69" s="4"/>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S69" s="4"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C70" s="3">
-        <v>3</v>
-      </c>
-      <c r="D70" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D70" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" s="3">
         <v>1</v>
@@ -4002,33 +4019,31 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>1</v>
-      </c>
-      <c r="M70" s="6"/>
-      <c r="N70" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N70" s="6"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
       <c r="R70" s="4"/>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S70" s="4"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C71" s="3">
-        <v>3</v>
-      </c>
-      <c r="D71" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D71" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E71">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F71" s="3">
         <v>1</v>
@@ -4050,30 +4065,28 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>1</v>
-      </c>
-      <c r="M71" s="6"/>
-      <c r="N71" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="N71" s="6"/>
       <c r="O71" s="4"/>
-      <c r="P71" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
       <c r="R71" s="4"/>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S71" s="4"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C72" s="3">
-        <v>3</v>
-      </c>
-      <c r="D72" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D72" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E72">
         <v>10</v>
@@ -4098,33 +4111,26 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>1</v>
-      </c>
-      <c r="M72" s="6"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C73" s="3">
-        <v>3</v>
-      </c>
-      <c r="D73" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D73" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E73">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F73" s="3">
         <v>1</v>
@@ -4146,33 +4152,26 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>1</v>
-      </c>
-      <c r="M73" s="6"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C74" s="3">
-        <v>3</v>
-      </c>
-      <c r="D74" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D74" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E74">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F74" s="3">
         <v>1</v>
@@ -4196,31 +4195,31 @@
       <c r="L74">
         <v>1</v>
       </c>
-      <c r="M74" s="6"/>
-      <c r="N74" s="4"/>
+      <c r="N74" s="6"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="4" t="s">
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q74" s="4"/>
       <c r="R74" s="4"/>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S74" s="4"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C75" s="3">
-        <v>3</v>
-      </c>
-      <c r="D75" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>2</v>
+      </c>
+      <c r="D75" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
       </c>
       <c r="E75">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F75" s="3">
         <v>1</v>
@@ -4244,31 +4243,31 @@
       <c r="L75">
         <v>1</v>
       </c>
-      <c r="M75" s="6"/>
-      <c r="N75" s="4"/>
+      <c r="N75" s="6"/>
       <c r="O75" s="4"/>
-      <c r="P75" s="4" t="s">
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q75" s="4"/>
       <c r="R75" s="4"/>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S75" s="4"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C76" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F76" s="3">
         <v>1</v>
@@ -4278,7 +4277,7 @@
         <v>基本</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -4292,31 +4291,31 @@
       <c r="L76">
         <v>1</v>
       </c>
-      <c r="M76" s="6"/>
-      <c r="N76" s="4"/>
+      <c r="N76" s="6"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="4" t="s">
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q76" s="4"/>
       <c r="R76" s="4"/>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S76" s="4"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C77" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E77">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F77" s="3">
         <v>1</v>
@@ -4326,7 +4325,7 @@
         <v>基本</v>
       </c>
       <c r="H77">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -4340,28 +4339,28 @@
       <c r="L77">
         <v>1</v>
       </c>
-      <c r="M77" s="6"/>
-      <c r="N77" s="4"/>
+      <c r="N77" s="6"/>
       <c r="O77" s="4"/>
-      <c r="P77" s="4" t="s">
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q77" s="4"/>
       <c r="R77" s="4"/>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S77" s="4"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C78" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E78">
         <v>10</v>
@@ -4374,7 +4373,7 @@
         <v>基本</v>
       </c>
       <c r="H78">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -4388,18 +4387,18 @@
       <c r="L78">
         <v>1</v>
       </c>
-      <c r="M78" s="6"/>
-      <c r="N78" s="4"/>
+      <c r="N78" s="6"/>
       <c r="O78" s="4"/>
-      <c r="P78" s="4" t="s">
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q78" s="4"/>
       <c r="R78" s="4"/>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S78" s="4"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>13</v>
@@ -4412,7 +4411,7 @@
         <v>♦</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F79" s="3">
         <v>1</v>
@@ -4422,7 +4421,7 @@
         <v>基本</v>
       </c>
       <c r="H79">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -4436,31 +4435,31 @@
       <c r="L79">
         <v>1</v>
       </c>
-      <c r="M79" s="6"/>
-      <c r="N79" s="4"/>
+      <c r="N79" s="6"/>
       <c r="O79" s="4"/>
-      <c r="P79" s="4" t="s">
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q79" s="4"/>
       <c r="R79" s="4"/>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S79" s="4"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C80" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>♥</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F80" s="3">
         <v>1</v>
@@ -4470,7 +4469,7 @@
         <v>基本</v>
       </c>
       <c r="H80">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4484,31 +4483,31 @@
       <c r="L80">
         <v>1</v>
       </c>
-      <c r="M80" s="6"/>
-      <c r="N80" s="4"/>
+      <c r="N80" s="6"/>
       <c r="O80" s="4"/>
-      <c r="P80" s="4" t="s">
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q80" s="4"/>
       <c r="R80" s="4"/>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S80" s="4"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C81" s="3">
-        <v>3</v>
-      </c>
-      <c r="D81" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D81" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E81">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F81" s="3">
         <v>1</v>
@@ -4518,7 +4517,7 @@
         <v>基本</v>
       </c>
       <c r="H81">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -4532,24 +4531,31 @@
       <c r="L81">
         <v>1</v>
       </c>
-      <c r="M81" s="6"/>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N81" s="6"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R81" s="4"/>
+      <c r="S81" s="4"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C82" s="3">
-        <v>3</v>
-      </c>
-      <c r="D82" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D82" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F82" s="3">
         <v>1</v>
@@ -4559,7 +4565,7 @@
         <v>基本</v>
       </c>
       <c r="H82">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -4573,24 +4579,31 @@
       <c r="L82">
         <v>1</v>
       </c>
-      <c r="M82" s="6"/>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N82" s="6"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R82" s="4"/>
+      <c r="S82" s="4"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C83" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E83">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F83" s="3">
         <v>1</v>
@@ -4600,7 +4613,7 @@
         <v>基本</v>
       </c>
       <c r="H83">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4614,24 +4627,31 @@
       <c r="L83">
         <v>1</v>
       </c>
-      <c r="M83" s="6"/>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N83" s="6"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R83" s="4"/>
+      <c r="S83" s="4"/>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C84" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E84">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F84" s="3">
         <v>1</v>
@@ -4641,7 +4661,7 @@
         <v>基本</v>
       </c>
       <c r="H84">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4655,24 +4675,31 @@
       <c r="L84">
         <v>1</v>
       </c>
-      <c r="M84" s="6"/>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N84" s="6"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R84" s="4"/>
+      <c r="S84" s="4"/>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C85" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E85">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F85" s="3">
         <v>1</v>
@@ -4682,7 +4709,7 @@
         <v>基本</v>
       </c>
       <c r="H85">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4696,11 +4723,18 @@
       <c r="L85">
         <v>1</v>
       </c>
-      <c r="M85" s="6"/>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N85" s="6"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R85" s="4"/>
+      <c r="S85" s="4"/>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>13</v>
@@ -4723,7 +4757,7 @@
         <v>基本</v>
       </c>
       <c r="H86">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4737,11 +4771,18 @@
       <c r="L86">
         <v>1</v>
       </c>
-      <c r="M86" s="6"/>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N86" s="6"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R86" s="4"/>
+      <c r="S86" s="4"/>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>13</v>
@@ -4764,7 +4805,7 @@
         <v>基本</v>
       </c>
       <c r="H87">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4778,11 +4819,18 @@
       <c r="L87">
         <v>1</v>
       </c>
-      <c r="M87" s="6"/>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N87" s="6"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R87" s="4"/>
+      <c r="S87" s="4"/>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>13</v>
@@ -4805,7 +4853,7 @@
         <v>基本</v>
       </c>
       <c r="H88">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4819,11 +4867,18 @@
       <c r="L88">
         <v>1</v>
       </c>
-      <c r="M88" s="6"/>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N88" s="6"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R88" s="4"/>
+      <c r="S88" s="4"/>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>13</v>
@@ -4846,7 +4901,7 @@
         <v>基本</v>
       </c>
       <c r="H89">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4860,24 +4915,31 @@
       <c r="L89">
         <v>1</v>
       </c>
-      <c r="M89" s="6"/>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="N89" s="6"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R89" s="4"/>
+      <c r="S89" s="4"/>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C90" s="3">
-        <v>2</v>
-      </c>
-      <c r="D90" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D90" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F90" s="3">
         <v>1</v>
@@ -4899,32 +4961,34 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>2</v>
-      </c>
-      <c r="M90" s="6"/>
-      <c r="N90" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N90" s="6"/>
       <c r="O90" s="4"/>
       <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
+      <c r="Q90" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R90" s="4"/>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S90" s="4"/>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="3">
+        <v>4</v>
+      </c>
+      <c r="D91" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E91">
         <v>10</v>
       </c>
-      <c r="C91" s="3">
-        <v>2</v>
-      </c>
-      <c r="D91" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E91">
-        <v>11</v>
-      </c>
       <c r="F91" s="3">
         <v>1</v>
       </c>
@@ -4945,31 +5009,33 @@
         <v>0</v>
       </c>
       <c r="L91">
-        <v>2</v>
-      </c>
-      <c r="M91" s="6"/>
-      <c r="N91" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N91" s="6"/>
       <c r="O91" s="4"/>
       <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
+      <c r="Q91" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R91" s="4"/>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S91" s="4"/>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C92" s="3">
-        <v>2</v>
-      </c>
-      <c r="D92" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D92" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E92">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F92" s="3">
         <v>1</v>
@@ -4991,31 +5057,33 @@
         <v>0</v>
       </c>
       <c r="L92">
-        <v>2</v>
-      </c>
-      <c r="M92" s="6"/>
-      <c r="N92" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N92" s="6"/>
       <c r="O92" s="4"/>
       <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
+      <c r="Q92" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R92" s="4"/>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S92" s="4"/>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C93" s="3">
-        <v>2</v>
-      </c>
-      <c r="D93" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D93" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E93">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F93" s="3">
         <v>1</v>
@@ -5037,31 +5105,33 @@
         <v>0</v>
       </c>
       <c r="L93">
-        <v>2</v>
-      </c>
-      <c r="M93" s="6"/>
-      <c r="N93" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N93" s="6"/>
       <c r="O93" s="4"/>
       <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
+      <c r="Q93" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R93" s="4"/>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S93" s="4"/>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C94" s="3">
-        <v>2</v>
-      </c>
-      <c r="D94" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D94" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E94">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F94" s="3">
         <v>1</v>
@@ -5083,32 +5153,34 @@
         <v>0</v>
       </c>
       <c r="L94">
-        <v>2</v>
-      </c>
-      <c r="M94" s="6"/>
-      <c r="N94" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N94" s="6"/>
       <c r="O94" s="4"/>
       <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
+      <c r="Q94" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R94" s="4"/>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S94" s="4"/>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="3">
+        <v>4</v>
+      </c>
+      <c r="D95" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E95">
         <v>10</v>
       </c>
-      <c r="C95" s="3">
-        <v>2</v>
-      </c>
-      <c r="D95" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E95">
-        <v>5</v>
-      </c>
       <c r="F95" s="3">
         <v>1</v>
       </c>
@@ -5129,31 +5201,33 @@
         <v>0</v>
       </c>
       <c r="L95">
-        <v>2</v>
-      </c>
-      <c r="M95" s="6"/>
-      <c r="N95" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N95" s="6"/>
       <c r="O95" s="4"/>
       <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
+      <c r="Q95" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R95" s="4"/>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S95" s="4"/>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C96" s="3">
-        <v>2</v>
-      </c>
-      <c r="D96" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D96" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E96">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F96" s="3">
         <v>1</v>
@@ -5175,28 +5249,30 @@
         <v>0</v>
       </c>
       <c r="L96">
-        <v>2</v>
-      </c>
-      <c r="M96" s="6"/>
-      <c r="N96" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N96" s="6"/>
       <c r="O96" s="4"/>
       <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
+      <c r="Q96" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R96" s="4"/>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S96" s="4"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C97" s="3">
-        <v>2</v>
-      </c>
-      <c r="D97" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D97" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E97">
         <v>7</v>
@@ -5221,28 +5297,30 @@
         <v>0</v>
       </c>
       <c r="L97">
-        <v>2</v>
-      </c>
-      <c r="M97" s="6"/>
-      <c r="N97" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N97" s="6"/>
       <c r="O97" s="4"/>
       <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
+      <c r="Q97" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R97" s="4"/>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S97" s="4"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C98" s="3">
-        <v>2</v>
-      </c>
-      <c r="D98" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D98" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E98">
         <v>8</v>
@@ -5267,28 +5345,30 @@
         <v>0</v>
       </c>
       <c r="L98">
-        <v>2</v>
-      </c>
-      <c r="M98" s="6"/>
-      <c r="N98" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N98" s="6"/>
       <c r="O98" s="4"/>
       <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
+      <c r="Q98" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R98" s="4"/>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S98" s="4"/>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C99" s="3">
-        <v>2</v>
-      </c>
-      <c r="D99" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D99" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E99">
         <v>9</v>
@@ -5313,28 +5393,30 @@
         <v>0</v>
       </c>
       <c r="L99">
-        <v>2</v>
-      </c>
-      <c r="M99" s="6"/>
-      <c r="N99" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N99" s="6"/>
       <c r="O99" s="4"/>
       <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
+      <c r="Q99" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R99" s="4"/>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S99" s="4"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C100" s="3">
-        <v>2</v>
-      </c>
-      <c r="D100" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D100" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E100">
         <v>10</v>
@@ -5359,31 +5441,33 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>2</v>
-      </c>
-      <c r="M100" s="6"/>
-      <c r="N100" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N100" s="6"/>
       <c r="O100" s="4"/>
       <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
+      <c r="Q100" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R100" s="4"/>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S100" s="4"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C101" s="3">
-        <v>2</v>
-      </c>
-      <c r="D101" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D101" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E101">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F101" s="3">
         <v>1</v>
@@ -5405,31 +5489,33 @@
         <v>0</v>
       </c>
       <c r="L101">
-        <v>2</v>
-      </c>
-      <c r="M101" s="6"/>
-      <c r="N101" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N101" s="6"/>
       <c r="O101" s="4"/>
       <c r="P101" s="4"/>
-      <c r="Q101" s="4"/>
+      <c r="Q101" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R101" s="4"/>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S101" s="4"/>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C102" s="3">
-        <v>1</v>
-      </c>
-      <c r="D102" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D102" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F102" s="3">
         <v>1</v>
@@ -5451,32 +5537,34 @@
         <v>0</v>
       </c>
       <c r="L102">
-        <v>2</v>
-      </c>
-      <c r="M102" s="6"/>
-      <c r="N102" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N102" s="6"/>
       <c r="O102" s="4"/>
       <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
+      <c r="Q102" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R102" s="4"/>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S102" s="4"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="3">
+        <v>3</v>
+      </c>
+      <c r="D103" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E103">
         <v>10</v>
       </c>
-      <c r="C103" s="3">
-        <v>1</v>
-      </c>
-      <c r="D103" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E103">
-        <v>13</v>
-      </c>
       <c r="F103" s="3">
         <v>1</v>
       </c>
@@ -5497,21 +5585,23 @@
         <v>0</v>
       </c>
       <c r="L103">
-        <v>2</v>
-      </c>
-      <c r="M103" s="6"/>
-      <c r="N103" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N103" s="6"/>
       <c r="O103" s="4"/>
       <c r="P103" s="4"/>
-      <c r="Q103" s="4"/>
+      <c r="Q103" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R103" s="4"/>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S103" s="4"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C104" s="3">
         <v>1</v>
@@ -5521,7 +5611,7 @@
         <v>♥</v>
       </c>
       <c r="E104">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
@@ -5531,7 +5621,7 @@
         <v>基本</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -5543,21 +5633,23 @@
         <v>0</v>
       </c>
       <c r="L104">
-        <v>2</v>
-      </c>
-      <c r="M104" s="6"/>
-      <c r="N104" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N104" s="6"/>
       <c r="O104" s="4"/>
       <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
+      <c r="Q104" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R104" s="4"/>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S104" s="4"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C105" s="3">
         <v>1</v>
@@ -5567,7 +5659,7 @@
         <v>♥</v>
       </c>
       <c r="E105">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F105" s="3">
         <v>1</v>
@@ -5577,7 +5669,7 @@
         <v>基本</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -5589,32 +5681,34 @@
         <v>0</v>
       </c>
       <c r="L105">
-        <v>2</v>
-      </c>
-      <c r="M105" s="6"/>
-      <c r="N105" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N105" s="6"/>
       <c r="O105" s="4"/>
       <c r="P105" s="4"/>
-      <c r="Q105" s="4"/>
+      <c r="Q105" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R105" s="4"/>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S105" s="4"/>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
+      </c>
+      <c r="E106">
         <v>10</v>
       </c>
-      <c r="C106" s="3">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E106">
-        <v>9</v>
-      </c>
       <c r="F106" s="3">
         <v>1</v>
       </c>
@@ -5623,7 +5717,7 @@
         <v>基本</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -5635,31 +5729,33 @@
         <v>0</v>
       </c>
       <c r="L106">
-        <v>2</v>
-      </c>
-      <c r="M106" s="6"/>
-      <c r="N106" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N106" s="6"/>
       <c r="O106" s="4"/>
       <c r="P106" s="4"/>
-      <c r="Q106" s="4"/>
+      <c r="Q106" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R106" s="4"/>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S106" s="4"/>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C107" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E107">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F107" s="3">
         <v>1</v>
@@ -5669,7 +5765,7 @@
         <v>基本</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -5681,31 +5777,33 @@
         <v>0</v>
       </c>
       <c r="L107">
-        <v>2</v>
-      </c>
-      <c r="M107" s="6"/>
-      <c r="N107" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N107" s="6"/>
       <c r="O107" s="4"/>
       <c r="P107" s="4"/>
-      <c r="Q107" s="4"/>
+      <c r="Q107" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R107" s="4"/>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S107" s="4"/>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C108" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E108">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F108" s="3">
         <v>1</v>
@@ -5715,7 +5813,7 @@
         <v>基本</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -5727,211 +5825,210 @@
         <v>0</v>
       </c>
       <c r="L108">
-        <v>2</v>
-      </c>
-      <c r="M108" s="6"/>
-      <c r="N108" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="N108" s="6"/>
       <c r="O108" s="4"/>
       <c r="P108" s="4"/>
-      <c r="Q108" s="4"/>
+      <c r="Q108" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="R108" s="4"/>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S108" s="4"/>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C109" s="3">
-        <v>2</v>
-      </c>
-      <c r="D109" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D109" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E109">
+        <v>4</v>
+      </c>
+      <c r="F109" s="3">
+        <v>1</v>
+      </c>
+      <c r="G109" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>基本</v>
+      </c>
+      <c r="H109">
+        <v>7</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="N109" s="6"/>
+      <c r="Q109" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>139</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="3">
+        <v>3</v>
+      </c>
+      <c r="D110" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E110">
+        <v>5</v>
+      </c>
+      <c r="F110" s="3">
+        <v>1</v>
+      </c>
+      <c r="G110" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>基本</v>
+      </c>
+      <c r="H110">
+        <v>7</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="N110" s="6"/>
+      <c r="Q110" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>140</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="3">
+        <v>3</v>
+      </c>
+      <c r="D111" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E111">
         <v>6</v>
       </c>
-      <c r="F109" s="3">
-        <v>1</v>
-      </c>
-      <c r="G109" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H109">
-        <v>0</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="K109">
-        <v>0</v>
-      </c>
-      <c r="L109">
-        <v>2</v>
-      </c>
-      <c r="M109" s="6"/>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
-      <c r="Q109" s="4"/>
-      <c r="R109" s="4"/>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A110">
-        <v>128</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110" s="3">
-        <v>2</v>
-      </c>
-      <c r="D110" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E110">
+      <c r="F111" s="3">
+        <v>1</v>
+      </c>
+      <c r="G111" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>基本</v>
+      </c>
+      <c r="H111">
         <v>7</v>
       </c>
-      <c r="F110" s="3">
-        <v>1</v>
-      </c>
-      <c r="G110" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H110">
-        <v>0</v>
-      </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>0</v>
-      </c>
-      <c r="L110">
-        <v>2</v>
-      </c>
-      <c r="M110" s="6"/>
-      <c r="N110" s="4"/>
-      <c r="O110" s="4"/>
-      <c r="P110" s="4"/>
-      <c r="Q110" s="4"/>
-      <c r="R110" s="4"/>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A111">
-        <v>129</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C111" s="3">
-        <v>2</v>
-      </c>
-      <c r="D111" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E111">
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="N111" s="6"/>
+      <c r="Q111" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>141</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="3">
+        <v>3</v>
+      </c>
+      <c r="D112" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E112">
+        <v>7</v>
+      </c>
+      <c r="F112" s="3">
+        <v>1</v>
+      </c>
+      <c r="G112" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>基本</v>
+      </c>
+      <c r="H112">
+        <v>7</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="N112" s="6"/>
+      <c r="Q112" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>142</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="3">
+        <v>3</v>
+      </c>
+      <c r="D113" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E113">
         <v>8</v>
       </c>
-      <c r="F111" s="3">
-        <v>1</v>
-      </c>
-      <c r="G111" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>2</v>
-      </c>
-      <c r="M111" s="6"/>
-      <c r="N111" s="4"/>
-      <c r="O111" s="4"/>
-      <c r="P111" s="4"/>
-      <c r="Q111" s="4"/>
-      <c r="R111" s="4"/>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A112">
-        <v>131</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C112" s="3">
-        <v>2</v>
-      </c>
-      <c r="D112" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E112">
-        <v>10</v>
-      </c>
-      <c r="F112" s="3">
-        <v>1</v>
-      </c>
-      <c r="G112" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>0</v>
-      </c>
-      <c r="L112">
-        <v>2</v>
-      </c>
-      <c r="M112" s="6"/>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A113">
-        <v>132</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C113" s="3">
-        <v>2</v>
-      </c>
-      <c r="D113" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E113">
-        <v>11</v>
-      </c>
       <c r="F113" s="3">
         <v>1</v>
       </c>
@@ -5940,7 +6037,7 @@
         <v>基本</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -5952,36 +6049,39 @@
         <v>0</v>
       </c>
       <c r="L113">
-        <v>2</v>
-      </c>
-      <c r="M113" s="6"/>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="N113" s="6"/>
+      <c r="Q113" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C114" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D114" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F114" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H114">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -5993,43 +6093,39 @@
         <v>0</v>
       </c>
       <c r="L114">
-        <v>11</v>
-      </c>
-      <c r="M114" s="6"/>
-      <c r="N114" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O114" s="4"/>
-      <c r="P114" s="4"/>
-      <c r="Q114" s="4"/>
-      <c r="R114" s="4"/>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="N114" s="6"/>
+      <c r="Q114" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C115" s="3">
-        <v>1</v>
-      </c>
-      <c r="D115" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>4</v>
+      </c>
+      <c r="D115" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E115">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F115" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G115" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H115">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -6041,43 +6137,39 @@
         <v>0</v>
       </c>
       <c r="L115">
-        <v>11</v>
-      </c>
-      <c r="M115" s="6"/>
-      <c r="N115" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O115" s="4"/>
-      <c r="P115" s="4"/>
-      <c r="Q115" s="4"/>
-      <c r="R115" s="4"/>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+      <c r="N115" s="6"/>
+      <c r="Q115" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C116" s="3">
-        <v>2</v>
-      </c>
-      <c r="D116" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D116" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E116">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F116" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G116" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -6089,99 +6181,83 @@
         <v>0</v>
       </c>
       <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="N116" s="6"/>
+      <c r="Q116" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>155</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" s="3">
         <v>4</v>
       </c>
-      <c r="M116" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N116" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O116" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P116" s="4"/>
-      <c r="Q116" s="4"/>
-      <c r="R116" s="4"/>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A117">
+      <c r="D117" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E117">
+        <v>8</v>
+      </c>
+      <c r="F117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G117" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>基本</v>
+      </c>
+      <c r="H117">
+        <v>7</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="N117" s="6"/>
+      <c r="Q117" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>107</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C118" s="3">
         <v>4</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C117" s="3">
-        <v>2</v>
-      </c>
-      <c r="D117" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E117">
-        <v>4</v>
-      </c>
-      <c r="F117" s="3">
-        <v>2</v>
-      </c>
-      <c r="G117" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>0</v>
-      </c>
-      <c r="L117">
-        <v>4</v>
-      </c>
-      <c r="M117" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N117" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O117" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P117" s="4"/>
-      <c r="Q117" s="4"/>
-      <c r="R117" s="4"/>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A118">
-        <v>81</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C118" s="3">
-        <v>3</v>
-      </c>
       <c r="D118" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F118" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G118" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -6193,27 +6269,21 @@
         <v>0</v>
       </c>
       <c r="L118">
-        <v>4</v>
-      </c>
-      <c r="M118" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N118" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O118" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N118" s="6"/>
+      <c r="O118" s="4"/>
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
       <c r="R118" s="4"/>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S118" s="4"/>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C119" s="3">
         <v>3</v>
@@ -6223,20 +6293,20 @@
         <v>♠</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F119" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G119" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6245,27 +6315,21 @@
         <v>0</v>
       </c>
       <c r="L119">
-        <v>4</v>
-      </c>
-      <c r="M119" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N119" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O119" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="N119" s="6"/>
+      <c r="O119" s="4"/>
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
       <c r="R119" s="4"/>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S119" s="4"/>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C120" s="3">
         <v>3</v>
@@ -6275,20 +6339,20 @@
         <v>♠</v>
       </c>
       <c r="E120">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F120" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G120" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6297,50 +6361,44 @@
         <v>0</v>
       </c>
       <c r="L120">
-        <v>4</v>
-      </c>
-      <c r="M120" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N120" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O120" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="N120" s="6"/>
+      <c r="O120" s="4"/>
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
       <c r="R120" s="4"/>
-    </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S120" s="4"/>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121">
+        <v>44</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C121" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>♥</v>
       </c>
       <c r="E121">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F121" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G121" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>装备</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6349,235 +6407,249 @@
         <v>0</v>
       </c>
       <c r="L121">
-        <v>3</v>
-      </c>
-      <c r="M121" s="6"/>
-      <c r="N121" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="N121" s="6"/>
       <c r="O121" s="4"/>
       <c r="P121" s="4"/>
-      <c r="Q121" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="Q121" s="4"/>
       <c r="R121" s="4"/>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S121" s="4"/>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C122" s="3">
-        <v>1</v>
-      </c>
-      <c r="D122" s="2" t="str">
+        <v>4</v>
+      </c>
+      <c r="D122" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E122">
+        <v>7</v>
+      </c>
+      <c r="F122" s="3">
+        <v>2</v>
+      </c>
+      <c r="G122" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>9</v>
+      </c>
+      <c r="M122" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N122" s="6"/>
+      <c r="O122" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P122" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q122" s="4"/>
+      <c r="R122" s="4"/>
+      <c r="S122" s="4"/>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>91</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123" s="3">
+        <v>3</v>
+      </c>
+      <c r="D123" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E123">
+        <v>13</v>
+      </c>
+      <c r="F123" s="3">
+        <v>2</v>
+      </c>
+      <c r="G123" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>9</v>
+      </c>
+      <c r="M123" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N123" s="6"/>
+      <c r="O123" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P123" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="4"/>
+      <c r="S123" s="4"/>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>98</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124" s="3">
+        <v>3</v>
+      </c>
+      <c r="D124" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E124">
+        <v>7</v>
+      </c>
+      <c r="F124" s="3">
+        <v>2</v>
+      </c>
+      <c r="G124" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>9</v>
+      </c>
+      <c r="M124" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N124" s="6"/>
+      <c r="O124" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P124" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4"/>
+      <c r="S124" s="4"/>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>32</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" s="3">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
         <v>♥</v>
       </c>
-      <c r="E122">
-        <v>3</v>
-      </c>
-      <c r="F122" s="3">
-        <v>1</v>
-      </c>
-      <c r="G122" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>3</v>
-      </c>
-      <c r="M122" s="6"/>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-      <c r="P122" s="4"/>
-      <c r="Q122" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R122" s="4"/>
-    </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A123">
-        <v>43</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C123" s="3">
-        <v>1</v>
-      </c>
-      <c r="D123" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E123">
+      <c r="E125">
+        <v>6</v>
+      </c>
+      <c r="F125" s="3">
+        <v>2</v>
+      </c>
+      <c r="G125" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H125">
+        <v>5</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>15</v>
+      </c>
+      <c r="M125" s="5"/>
+      <c r="N125" s="6"/>
+      <c r="O125" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P125" s="4"/>
+      <c r="Q125" s="4"/>
+      <c r="R125" s="4"/>
+      <c r="S125" s="4"/>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>71</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="3">
         <v>4</v>
       </c>
-      <c r="F123" s="3">
-        <v>1</v>
-      </c>
-      <c r="G123" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>3</v>
-      </c>
-      <c r="M123" s="6"/>
-      <c r="N123" s="4"/>
-      <c r="O123" s="4"/>
-      <c r="P123" s="4"/>
-      <c r="Q123" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R123" s="4"/>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A124">
-        <v>45</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C124" s="3">
-        <v>1</v>
-      </c>
-      <c r="D124" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E124">
+      <c r="D126" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E126">
         <v>6</v>
       </c>
-      <c r="F124" s="3">
-        <v>1</v>
-      </c>
-      <c r="G124" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>3</v>
-      </c>
-      <c r="M124" s="6"/>
-      <c r="N124" s="4"/>
-      <c r="O124" s="4"/>
-      <c r="P124" s="4"/>
-      <c r="Q124" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R124" s="4"/>
-    </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A125">
-        <v>46</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" s="3">
-        <v>1</v>
-      </c>
-      <c r="D125" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E125">
-        <v>7</v>
-      </c>
-      <c r="F125" s="3">
-        <v>1</v>
-      </c>
-      <c r="G125" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>3</v>
-      </c>
-      <c r="M125" s="6"/>
-      <c r="N125" s="4"/>
-      <c r="O125" s="4"/>
-      <c r="P125" s="4"/>
-      <c r="Q125" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R125" s="4"/>
-    </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A126">
-        <v>47</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C126" s="3">
-        <v>1</v>
-      </c>
-      <c r="D126" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E126">
-        <v>8</v>
-      </c>
       <c r="F126" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G126" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -6589,43 +6661,44 @@
         <v>0</v>
       </c>
       <c r="L126">
-        <v>3</v>
-      </c>
-      <c r="M126" s="6"/>
-      <c r="N126" s="4"/>
-      <c r="O126" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="M126" s="5"/>
+      <c r="N126" s="6"/>
+      <c r="O126" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="P126" s="4"/>
-      <c r="Q126" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="Q126" s="4"/>
       <c r="R126" s="4"/>
-    </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S126" s="4"/>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C127" s="3">
-        <v>1</v>
-      </c>
-      <c r="D127" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D127" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E127">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F127" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G127" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -6637,43 +6710,44 @@
         <v>0</v>
       </c>
       <c r="L127">
-        <v>3</v>
-      </c>
-      <c r="M127" s="6"/>
-      <c r="N127" s="4"/>
-      <c r="O127" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="M127" s="5"/>
+      <c r="N127" s="6"/>
+      <c r="O127" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="P127" s="4"/>
-      <c r="Q127" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="Q127" s="4"/>
       <c r="R127" s="4"/>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S127" s="4"/>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C128" s="3">
-        <v>1</v>
-      </c>
-      <c r="D128" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D128" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E128">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F128" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G128" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>装备</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -6682,43 +6756,41 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128">
-        <v>3</v>
-      </c>
-      <c r="M128" s="6"/>
-      <c r="N128" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="N128" s="6"/>
       <c r="O128" s="4"/>
       <c r="P128" s="4"/>
-      <c r="Q128" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="Q128" s="4"/>
       <c r="R128" s="4"/>
-    </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S128" s="4"/>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C129" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E129">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F129" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G129" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -6733,40 +6805,45 @@
         <v>0</v>
       </c>
       <c r="L129">
-        <v>3</v>
-      </c>
-      <c r="M129" s="6"/>
-      <c r="N129" s="4"/>
-      <c r="O129" s="4"/>
-      <c r="P129" s="4"/>
-      <c r="Q129" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M129" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N129" s="6"/>
+      <c r="O129" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P129" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q129" s="4"/>
       <c r="R129" s="4"/>
-    </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S129" s="4"/>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C130" s="3">
-        <v>1</v>
-      </c>
-      <c r="D130" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>4</v>
+      </c>
+      <c r="D130" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E130">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F130" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
+        <v>锦囊</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -6781,81 +6858,91 @@
         <v>0</v>
       </c>
       <c r="L130">
-        <v>3</v>
-      </c>
-      <c r="M130" s="6"/>
-      <c r="N130" s="4"/>
-      <c r="O130" s="4"/>
-      <c r="P130" s="4"/>
-      <c r="Q130" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M130" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N130" s="6"/>
+      <c r="O130" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P130" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q130" s="4"/>
       <c r="R130" s="4"/>
-    </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S130" s="4"/>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C131" s="3">
-        <v>2</v>
-      </c>
-      <c r="D131" s="2" t="str">
+        <v>3</v>
+      </c>
+      <c r="D131" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131" s="3">
+        <v>2</v>
+      </c>
+      <c r="G131" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>8</v>
+      </c>
+      <c r="M131" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N131" s="6"/>
+      <c r="O131" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P131" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q131" s="4"/>
+      <c r="R131" s="4"/>
+      <c r="S131" s="4"/>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C132" s="3">
+        <v>2</v>
+      </c>
+      <c r="D132" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
         <v>♦</v>
       </c>
-      <c r="E131">
-        <v>2</v>
-      </c>
-      <c r="F131" s="3">
-        <v>1</v>
-      </c>
-      <c r="G131" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>基本</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>3</v>
-      </c>
-      <c r="M131" s="6"/>
-      <c r="N131" s="4"/>
-      <c r="O131" s="4"/>
-      <c r="P131" s="4"/>
-      <c r="Q131" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R131" s="4"/>
-    </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A132">
-        <v>124</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C132" s="3">
-        <v>2</v>
-      </c>
-      <c r="D132" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
       <c r="E132">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F132" s="3">
         <v>1</v>
@@ -6877,40 +6964,40 @@
         <v>0</v>
       </c>
       <c r="L132">
-        <v>3</v>
-      </c>
-      <c r="M132" s="6"/>
-      <c r="N132" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="N132" s="6"/>
       <c r="O132" s="4"/>
       <c r="P132" s="4"/>
-      <c r="Q132" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="Q132" s="4"/>
       <c r="R132" s="4"/>
-    </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S132" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C133" s="3">
-        <v>1</v>
-      </c>
-      <c r="D133" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D133" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G133" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -6925,23 +7012,16 @@
         <v>0</v>
       </c>
       <c r="L133">
-        <v>12</v>
-      </c>
-      <c r="M133" s="6"/>
-      <c r="N133" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O133" s="4"/>
-      <c r="P133" s="4"/>
-      <c r="Q133" s="4"/>
-      <c r="R133" s="4"/>
-    </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+      <c r="N133" s="6"/>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C134" s="3">
         <v>3</v>
@@ -6951,17 +7031,17 @@
         <v>♠</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F134" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G134" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>基本</v>
       </c>
       <c r="H134">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -6973,16 +7053,16 @@
         <v>0</v>
       </c>
       <c r="L134">
-        <v>88</v>
-      </c>
-      <c r="M134" s="6"/>
-    </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C135" s="3">
         <v>4</v>
@@ -6992,17 +7072,17 @@
         <v>♣</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G135" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
+        <v>基本</v>
       </c>
       <c r="H135">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -7014,33 +7094,33 @@
         <v>0</v>
       </c>
       <c r="L135">
-        <v>88</v>
-      </c>
-      <c r="M135" s="6"/>
-    </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C136" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D136" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E136">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F136" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G136" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>基本</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -7055,25 +7135,23 @@
         <v>0</v>
       </c>
       <c r="L136">
-        <v>85</v>
-      </c>
-      <c r="M136" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+      <c r="N136" s="6"/>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C137" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D137" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E137">
         <v>12</v>
@@ -7098,18 +7176,24 @@
         <v>0</v>
       </c>
       <c r="L137">
-        <v>85</v>
-      </c>
-      <c r="M137" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+      <c r="M137" s="5"/>
+      <c r="N137" s="6"/>
+      <c r="O137" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P137" s="4"/>
+      <c r="Q137" s="4"/>
+      <c r="R137" s="4"/>
+      <c r="S137" s="4"/>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C138" s="3">
         <v>4</v>
@@ -7119,7 +7203,7 @@
         <v>♣</v>
       </c>
       <c r="E138">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F138" s="3">
         <v>2</v>
@@ -7141,28 +7225,34 @@
         <v>0</v>
       </c>
       <c r="L138">
-        <v>85</v>
-      </c>
-      <c r="M138" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+      <c r="M138" s="5"/>
+      <c r="N138" s="6"/>
+      <c r="O138" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P138" s="4"/>
+      <c r="Q138" s="4"/>
+      <c r="R138" s="4"/>
+      <c r="S138" s="4"/>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C139" s="3">
-        <v>4</v>
-      </c>
-      <c r="D139" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D139" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E139">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F139" s="3">
         <v>2</v>
@@ -7184,124 +7274,145 @@
         <v>0</v>
       </c>
       <c r="L139">
-        <v>85</v>
-      </c>
-      <c r="M139" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+      <c r="M139" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N139" s="6"/>
+      <c r="O139" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P139" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q139" s="4"/>
+      <c r="R139" s="4"/>
+      <c r="S139" s="4"/>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C140" s="3">
-        <v>4</v>
-      </c>
-      <c r="D140" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D140" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E140">
+        <v>3</v>
+      </c>
+      <c r="F140" s="3">
+        <v>2</v>
+      </c>
+      <c r="G140" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>83</v>
+      </c>
+      <c r="M140" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N140" s="6"/>
+      <c r="O140" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P140" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q140" s="4"/>
+      <c r="R140" s="4"/>
+      <c r="S140" s="4"/>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>133</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C141" s="3">
+        <v>2</v>
+      </c>
+      <c r="D141" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
+      </c>
+      <c r="E141">
         <v>12</v>
       </c>
-      <c r="F140" s="3">
-        <v>2</v>
-      </c>
-      <c r="G140" t="str">
+      <c r="F141" s="3">
+        <v>2</v>
+      </c>
+      <c r="G141" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
         <v>锦囊</v>
       </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>85</v>
-      </c>
-      <c r="M140" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A141">
-        <v>160</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C141" s="3">
-        <v>4</v>
-      </c>
-      <c r="D141" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
-      </c>
-      <c r="E141">
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>83</v>
+      </c>
+      <c r="M141" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N141" s="6"/>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>134</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C142" s="3">
+        <v>2</v>
+      </c>
+      <c r="D142" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♦</v>
+      </c>
+      <c r="E142">
         <v>13</v>
       </c>
-      <c r="F141" s="3">
-        <v>2</v>
-      </c>
-      <c r="G141" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>85</v>
-      </c>
-      <c r="M141" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A142">
-        <v>27</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C142" s="3">
-        <v>1</v>
-      </c>
-      <c r="D142" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E142">
-        <v>1</v>
-      </c>
       <c r="F142" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G142" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -7310,51 +7421,42 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142">
-        <v>10</v>
-      </c>
-      <c r="M142" s="6"/>
-      <c r="N142" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O142" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P142" s="4"/>
-      <c r="Q142" s="4"/>
-      <c r="R142" s="4"/>
-    </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+      <c r="N142" s="6"/>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C143" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D143" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>♠</v>
       </c>
       <c r="E143">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F143" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G143" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -7363,33 +7465,31 @@
         <v>0</v>
       </c>
       <c r="L143">
-        <v>13</v>
-      </c>
-      <c r="M143" s="6"/>
-      <c r="N143" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N143" s="6"/>
       <c r="O143" s="4"/>
       <c r="P143" s="4"/>
       <c r="Q143" s="4"/>
       <c r="R143" s="4"/>
-    </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S143" s="4"/>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C144" s="3">
-        <v>4</v>
-      </c>
-      <c r="D144" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♣</v>
+        <v>1</v>
+      </c>
+      <c r="D144" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E144">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F144" s="3">
         <v>2</v>
@@ -7411,33 +7511,38 @@
         <v>0</v>
       </c>
       <c r="L144">
-        <v>13</v>
-      </c>
-      <c r="M144" s="6"/>
-      <c r="N144" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M144" s="5"/>
+      <c r="N144" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O144" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O144" s="4"/>
-      <c r="P144" s="4"/>
+      <c r="P144" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q144" s="4"/>
       <c r="R144" s="4"/>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S144" s="4"/>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C145" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D145" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>♣</v>
       </c>
       <c r="E145">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F145" s="3">
         <v>2</v>
@@ -7459,33 +7564,38 @@
         <v>0</v>
       </c>
       <c r="L145">
-        <v>13</v>
-      </c>
-      <c r="M145" s="6"/>
-      <c r="N145" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M145" s="5"/>
+      <c r="N145" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O145" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O145" s="4"/>
-      <c r="P145" s="4"/>
+      <c r="P145" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q145" s="4"/>
       <c r="R145" s="4"/>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S145" s="4"/>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C146" s="3">
-        <v>2</v>
-      </c>
-      <c r="D146" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>4</v>
+      </c>
+      <c r="D146" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E146">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F146" s="3">
         <v>2</v>
@@ -7507,33 +7617,38 @@
         <v>0</v>
       </c>
       <c r="L146">
-        <v>13</v>
-      </c>
-      <c r="M146" s="6"/>
-      <c r="N146" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M146" s="5"/>
+      <c r="N146" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O146" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O146" s="4"/>
-      <c r="P146" s="4"/>
+      <c r="P146" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q146" s="4"/>
       <c r="R146" s="4"/>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S146" s="4"/>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C147" s="3">
-        <v>1</v>
-      </c>
-      <c r="D147" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D147" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E147">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F147" s="3">
         <v>2</v>
@@ -7555,33 +7670,38 @@
         <v>0</v>
       </c>
       <c r="L147">
-        <v>13</v>
-      </c>
-      <c r="M147" s="6"/>
-      <c r="N147" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M147" s="5"/>
+      <c r="N147" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O147" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O147" s="4"/>
-      <c r="P147" s="4"/>
+      <c r="P147" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q147" s="4"/>
       <c r="R147" s="4"/>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S147" s="4"/>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C148" s="3">
-        <v>1</v>
-      </c>
-      <c r="D148" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D148" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E148">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F148" s="3">
         <v>2</v>
@@ -7603,23 +7723,28 @@
         <v>0</v>
       </c>
       <c r="L148">
-        <v>13</v>
-      </c>
-      <c r="M148" s="6"/>
-      <c r="N148" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M148" s="5"/>
+      <c r="N148" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O148" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O148" s="4"/>
-      <c r="P148" s="4"/>
+      <c r="P148" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="Q148" s="4"/>
       <c r="R148" s="4"/>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S148" s="4"/>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C149" s="3">
         <v>3</v>
@@ -7629,7 +7754,7 @@
         <v>♠</v>
       </c>
       <c r="E149">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F149" s="3">
         <v>2</v>
@@ -7651,39 +7776,51 @@
         <v>0</v>
       </c>
       <c r="L149">
-        <v>13</v>
-      </c>
-      <c r="M149" s="6"/>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+      <c r="M149" s="5"/>
+      <c r="N149" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O149" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P149" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q149" s="4"/>
+      <c r="R149" s="4"/>
+      <c r="S149" s="4"/>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C150" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E150">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F150" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G150" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -7692,50 +7829,44 @@
         <v>0</v>
       </c>
       <c r="L150">
-        <v>7</v>
-      </c>
-      <c r="M150" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N150" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O150" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="N150" s="6"/>
+      <c r="O150" s="4"/>
       <c r="P150" s="4"/>
       <c r="Q150" s="4"/>
       <c r="R150" s="4"/>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S150" s="4"/>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C151" s="3">
-        <v>1</v>
-      </c>
-      <c r="D151" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D151" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E151">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F151" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G151" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J151">
         <v>0</v>
@@ -7744,50 +7875,39 @@
         <v>0</v>
       </c>
       <c r="L151">
-        <v>7</v>
-      </c>
-      <c r="M151" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N151" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O151" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P151" s="4"/>
-      <c r="Q151" s="4"/>
-      <c r="R151" s="4"/>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+      <c r="N151" s="6"/>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C152" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="2" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>♦</v>
       </c>
       <c r="E152">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F152" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G152" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J152">
         <v>0</v>
@@ -7796,47 +7916,41 @@
         <v>0</v>
       </c>
       <c r="L152">
-        <v>7</v>
-      </c>
-      <c r="M152" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N152" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O152" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N152" s="6"/>
+      <c r="O152" s="4"/>
       <c r="P152" s="4"/>
       <c r="Q152" s="4"/>
       <c r="R152" s="4"/>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S152" s="4"/>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C153" s="3">
-        <v>1</v>
-      </c>
-      <c r="D153" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>4</v>
+      </c>
+      <c r="D153" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
       </c>
       <c r="E153">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F153" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G153" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -7845,103 +7959,93 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153">
-        <v>7</v>
-      </c>
-      <c r="M153" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N153" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O153" s="5" t="s">
-        <v>54</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="N153" s="6"/>
+      <c r="O153" s="4"/>
       <c r="P153" s="4"/>
       <c r="Q153" s="4"/>
       <c r="R153" s="4"/>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S153" s="4"/>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C154" s="3">
+        <v>3</v>
+      </c>
+      <c r="D154" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
+      </c>
+      <c r="E154">
+        <v>13</v>
+      </c>
+      <c r="F154" s="3">
+        <v>3</v>
+      </c>
+      <c r="G154" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>装备</v>
+      </c>
+      <c r="H154">
+        <v>4</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
         <v>19</v>
       </c>
-      <c r="C154" s="3">
-        <v>1</v>
-      </c>
-      <c r="D154" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
-      </c>
-      <c r="E154">
-        <v>3</v>
-      </c>
-      <c r="F154" s="3">
-        <v>2</v>
-      </c>
-      <c r="G154" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
-      </c>
-      <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>6</v>
-      </c>
-      <c r="M154" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N154" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="N154" s="6"/>
       <c r="O154" s="4"/>
       <c r="P154" s="4"/>
       <c r="Q154" s="4"/>
       <c r="R154" s="4"/>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S154" s="4"/>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C155" s="3">
-        <v>1</v>
-      </c>
-      <c r="D155" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D155" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F155" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G155" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>锦囊</v>
+        <v>装备</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -7950,35 +8054,31 @@
         <v>0</v>
       </c>
       <c r="L155">
-        <v>6</v>
-      </c>
-      <c r="M155" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N155" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N155" s="6"/>
       <c r="O155" s="4"/>
       <c r="P155" s="4"/>
       <c r="Q155" s="4"/>
       <c r="R155" s="4"/>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S155" s="4"/>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C156" s="3">
-        <v>3</v>
-      </c>
-      <c r="D156" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♠</v>
+        <v>1</v>
+      </c>
+      <c r="D156" s="2" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♥</v>
       </c>
       <c r="E156">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F156" s="3">
         <v>3</v>
@@ -7988,148 +8088,138 @@
         <v>装备</v>
       </c>
       <c r="H156">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I156">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156">
         <v>0</v>
       </c>
       <c r="L156">
-        <v>27</v>
-      </c>
-      <c r="M156" s="6"/>
-      <c r="N156" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="N156" s="6"/>
       <c r="O156" s="4"/>
       <c r="P156" s="4"/>
       <c r="Q156" s="4"/>
       <c r="R156" s="4"/>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S156" s="4"/>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C157" s="3">
-        <v>1</v>
-      </c>
-      <c r="D157" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♥</v>
+        <v>3</v>
+      </c>
+      <c r="D157" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E157">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F157" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G157" t="str">
         <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H157">
+        <v>5</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>84</v>
+      </c>
+      <c r="N157" s="6"/>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>151</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C158" s="3">
+        <v>4</v>
+      </c>
+      <c r="D158" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E158">
+        <v>4</v>
+      </c>
+      <c r="F158" s="3">
+        <v>2</v>
+      </c>
+      <c r="G158" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
+        <v>锦囊</v>
+      </c>
+      <c r="H158">
+        <v>5</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>84</v>
+      </c>
+      <c r="N158" s="6"/>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>148</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C159" s="3">
+        <v>4</v>
+      </c>
+      <c r="D159" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♣</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159" s="3">
+        <v>3</v>
+      </c>
+      <c r="G159" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
         <v>装备</v>
       </c>
-      <c r="H157">
-        <v>3</v>
-      </c>
-      <c r="I157">
-        <v>0</v>
-      </c>
-      <c r="J157">
-        <v>0</v>
-      </c>
-      <c r="K157">
-        <v>1</v>
-      </c>
-      <c r="L157">
-        <v>22</v>
-      </c>
-      <c r="M157" s="6"/>
-      <c r="N157" s="4"/>
-      <c r="O157" s="4"/>
-      <c r="P157" s="4"/>
-      <c r="Q157" s="4"/>
-      <c r="R157" s="4"/>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A158">
-        <v>122</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C158" s="3">
-        <v>2</v>
-      </c>
-      <c r="D158" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E158">
-        <v>1</v>
-      </c>
-      <c r="F158" s="3">
-        <v>3</v>
-      </c>
-      <c r="G158" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
-      </c>
-      <c r="H158">
-        <v>1</v>
-      </c>
-      <c r="I158">
-        <v>4</v>
-      </c>
-      <c r="J158">
-        <v>0</v>
-      </c>
-      <c r="K158">
-        <v>0</v>
-      </c>
-      <c r="L158">
-        <v>87</v>
-      </c>
-      <c r="M158" s="6"/>
-      <c r="N158" s="4"/>
-      <c r="O158" s="4"/>
-      <c r="P158" s="4"/>
-      <c r="Q158" s="4"/>
-      <c r="R158" s="4"/>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A159">
-        <v>14</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" s="3">
-        <v>2</v>
-      </c>
-      <c r="D159" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
-      </c>
-      <c r="E159">
-        <v>1</v>
-      </c>
-      <c r="F159" s="3">
-        <v>3</v>
-      </c>
-      <c r="G159" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</f>
-        <v>装备</v>
-      </c>
       <c r="H159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -8138,21 +8228,16 @@
         <v>0</v>
       </c>
       <c r="L159">
-        <v>23</v>
-      </c>
-      <c r="M159" s="6"/>
-      <c r="N159" s="4"/>
-      <c r="O159" s="4"/>
-      <c r="P159" s="4"/>
-      <c r="Q159" s="4"/>
-      <c r="R159" s="4"/>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+      <c r="N159" s="6"/>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A160">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C160" s="3">
         <v>4</v>
@@ -8162,7 +8247,7 @@
         <v>♣</v>
       </c>
       <c r="E160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="3">
         <v>3</v>
@@ -8172,10 +8257,10 @@
         <v>装备</v>
       </c>
       <c r="H160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -8184,31 +8269,31 @@
         <v>0</v>
       </c>
       <c r="L160">
-        <v>23</v>
-      </c>
-      <c r="M160" s="6"/>
-      <c r="N160" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="N160" s="6"/>
       <c r="O160" s="4"/>
       <c r="P160" s="4"/>
       <c r="Q160" s="4"/>
       <c r="R160" s="4"/>
-    </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S160" s="4"/>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A161">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C161" s="3">
-        <v>2</v>
-      </c>
-      <c r="D161" s="2" t="str">
-        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
-        <v>♦</v>
+        <v>3</v>
+      </c>
+      <c r="D161" t="str">
+        <f>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</f>
+        <v>♠</v>
       </c>
       <c r="E161">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F161" s="3">
         <v>3</v>
@@ -8218,26 +8303,26 @@
         <v>装备</v>
       </c>
       <c r="H161">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I161">
         <v>0</v>
       </c>
       <c r="J161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161">
         <v>0</v>
       </c>
       <c r="L161">
-        <v>18</v>
-      </c>
-      <c r="M161" s="6"/>
-      <c r="N161" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="N161" s="6"/>
       <c r="O161" s="4"/>
       <c r="P161" s="4"/>
       <c r="Q161" s="4"/>
       <c r="R161" s="4"/>
+      <c r="S161" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
